--- a/www/flightdata/xlsx/eoss-366.xlsx
+++ b/www/flightdata/xlsx/eoss-366.xlsx
@@ -3069,7 +3069,7 @@
         <v>26864.16</v>
       </c>
       <c r="I2">
-        <v>586</v>
+        <v>375</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
